--- a/bom/RB_SWITCH_RevD_PCBWay_CPL.xlsx
+++ b/bom/RB_SWITCH_RevD_PCBWay_CPL.xlsx
@@ -399,12 +399,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>37.0000mm</t>
+          <t>13.0000mm</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-16.0000mm</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -449,12 +449,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>43.0000mm</t>
+          <t>13.0000mm</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-22.0000mm</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>U_CHG</t>
+          <t>U_CHG1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="4">
@@ -549,12 +549,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>73.0000mm</t>
+          <t>99.0000mm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-29.8000mm</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>79.0000mm</t>
+          <t>31.0000mm</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-27.0000mm</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>67.0000mm</t>
+          <t>95.0000mm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-29.8000mm</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>25.0000mm</t>
+          <t>49.6500mm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-13.0000mm</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -644,17 +644,17 @@
     <row r="12" ht="15" customHeight="1" s="4">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>SW_RST</t>
+          <t>SW_RST1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>15.0000mm</t>
+          <t>87.0000mm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-33.5000mm</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>31.0000mm</t>
+          <t>52.5000mm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-11.5000mm</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>61.0000mm</t>
+          <t>91.0000mm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-29.8000mm</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>85.0000mm</t>
+          <t>56.0000mm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-27.0000mm</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>73.0000mm</t>
+          <t>35.5000mm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-9.5000mm</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>61.0000mm</t>
+          <t>25.0000mm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-11.8000mm</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>91.0000mm</t>
+          <t>48.0000mm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-10.5000mm</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>55.0000mm</t>
+          <t>93.5000mm</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-33.5000mm</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="21" ht="15" customHeight="1" s="4">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>SW_BOOT</t>
+          <t>SW_BOOT1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>49.0000mm</t>
+          <t>103.4000mm</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-29.8000mm</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="23" ht="15" customHeight="1" s="4">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>J_USB</t>
+          <t>J_USB1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>49.0000mm</t>
+          <t>21.5000mm</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-11.8000mm</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>43.0000mm</t>
+          <t>29.5000mm</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-10.8000mm</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>67.0000mm</t>
+          <t>35.5000mm</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>-6.0000mm</t>
+          <t>-4.5000mm</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>91.0000mm</t>
+          <t>81.0000mm</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>-33.0000mm</t>
+          <t>-27.0000mm</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>55.0000mm</t>
+          <t>19.6000mm</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="4">
@@ -1072,22 +1072,22 @@
           <t>SW1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>25.2500mm</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>-21.2500mm</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1097,22 +1097,22 @@
           <t>SW2</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>50.2500mm</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>-21.2500mm</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1122,22 +1122,22 @@
           <t>SW3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>75.2500mm</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>-21.2500mm</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="6" t="n"/>
@@ -1145,26 +1145,26 @@
     <row r="32" ht="15" customHeight="1" s="4">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>J_BAT</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>38.0000mm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-8.4500mm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
+          <t>J_BAT1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>42.0000mm</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>-4.7500mm</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/bom/RB_SWITCH_RevD_PCBWay_CPL.xlsx
+++ b/bom/RB_SWITCH_RevD_PCBWay_CPL.xlsx
@@ -356,7 +356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="3" min="1" max="5"/>
@@ -1167,6 +1167,31 @@
         <v>180</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>104.2000mm</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-33.6000mm</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
